--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2014/SOUTH_CAROLINA_2014.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2014/SOUTH_CAROLINA_2014.xlsx
@@ -2814,7 +2814,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Gral. Simon Boivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C137">
@@ -4506,7 +4506,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C231">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C241">
@@ -10770,7 +10770,7 @@
       </c>
       <c r="B579" t="inlineStr">
         <is>
-          <t>Dr. Arroyo</t>
+          <t>Doctor Arroyo</t>
         </is>
       </c>
       <c r="C579">
@@ -12516,7 +12516,7 @@
       </c>
       <c r="B676" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C676">
@@ -13290,7 +13290,7 @@
       </c>
       <c r="B719" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C719">
@@ -21930,7 +21930,7 @@
       </c>
       <c r="B1199" t="inlineStr">
         <is>
-          <t>Tuxpam</t>
+          <t>Tuxpan</t>
         </is>
       </c>
       <c r="C1199">
